--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_individual_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_individual_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008450004899078973</v>
       </c>
       <c r="C2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>23185132</v>
+        <v>4328909</v>
       </c>
       <c r="L2" t="n">
-        <v>13867757</v>
+        <v>2355386</v>
       </c>
       <c r="M2" t="n">
-        <v>3509083</v>
+        <v>534164</v>
       </c>
       <c r="N2" t="n">
-        <v>186245</v>
+        <v>18895</v>
       </c>
       <c r="O2" t="n">
-        <v>2116587</v>
+        <v>350263</v>
       </c>
       <c r="P2" t="n">
-        <v>812362</v>
+        <v>127718</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999945163726807</v>
+        <v>0.9999933242797852</v>
       </c>
       <c r="R2" t="n">
-        <v>0.921545147895813</v>
+        <v>0.851405143737793</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8297766447067261</v>
+        <v>0.7041053771972656</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7945718765258789</v>
+        <v>0.6361246109008789</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5743516087532043</v>
+        <v>0.2667466700077057</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8264357447624207</v>
+        <v>0.6777744889259338</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8930676579475403</v>
+        <v>0.8002481460571289</v>
       </c>
       <c r="X2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="AG2" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AH2" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AI2" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565606117248535</v>
+        <v>0.9563109874725342</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112661480903625</v>
+        <v>0.9112939834594727</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580878376960754</v>
+        <v>0.8580310344696045</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623296141624451</v>
+        <v>0.6617932319641113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020044803619385</v>
+        <v>0.9019097685813904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026420486158906</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>23185132</v>
+        <v>4328909</v>
       </c>
       <c r="E3" t="n">
-        <v>1930931</v>
+        <v>676954</v>
       </c>
       <c r="F3" t="n">
-        <v>22432</v>
+        <v>10144</v>
       </c>
       <c r="G3" t="n">
-        <v>2530</v>
+        <v>722</v>
       </c>
       <c r="H3" t="n">
-        <v>1450</v>
+        <v>812</v>
       </c>
       <c r="I3" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="J3" t="n">
-        <v>50082937</v>
+        <v>10016580</v>
       </c>
       <c r="K3" t="n">
-        <v>54531616</v>
+        <v>10556507</v>
       </c>
       <c r="L3" t="n">
-        <v>62481943</v>
+        <v>12066341</v>
       </c>
       <c r="M3" t="n">
-        <v>76079468</v>
+        <v>15090629</v>
       </c>
       <c r="N3" t="n">
-        <v>81064328</v>
+        <v>16188402</v>
       </c>
       <c r="O3" t="n">
-        <v>78657618</v>
+        <v>15653527</v>
       </c>
       <c r="P3" t="n">
-        <v>80584146</v>
+        <v>16104327</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9221475720405579</v>
+        <v>0.8627495765686035</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8496788144111633</v>
+        <v>0.71954745054245</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7528127431869507</v>
+        <v>0.5722660422325134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4179204702377319</v>
+        <v>0.2116897106170654</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8313819169998169</v>
+        <v>0.6873940229415894</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8404454588890076</v>
+        <v>0.6604065299034119</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="Z3" t="n">
-        <v>989932</v>
+        <v>198330</v>
       </c>
       <c r="AA3" t="n">
-        <v>42706</v>
+        <v>8575</v>
       </c>
       <c r="AB3" t="n">
-        <v>33970</v>
+        <v>6824</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50083110</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>55412140</v>
+        <v>11092567</v>
       </c>
       <c r="AG3" t="n">
-        <v>63880556</v>
+        <v>12766203</v>
       </c>
       <c r="AH3" t="n">
-        <v>76325582</v>
+        <v>15263782</v>
       </c>
       <c r="AI3" t="n">
-        <v>81051985</v>
+        <v>16210177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78852750</v>
+        <v>15770083</v>
       </c>
       <c r="AK3" t="n">
-        <v>80615145</v>
+        <v>16122953</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575626254081726</v>
+        <v>0.9573889374732971</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100250601768494</v>
+        <v>0.9100300669670105</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576043844223022</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618287563323975</v>
+        <v>0.6612964868545532</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016448855400085</v>
+        <v>0.9016017913818359</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -929,282 +929,282 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1862322</v>
+        <v>713172</v>
       </c>
       <c r="E4" t="n">
-        <v>13867757</v>
+        <v>2355386</v>
       </c>
       <c r="F4" t="n">
-        <v>536625</v>
+        <v>178534</v>
       </c>
       <c r="G4" t="n">
-        <v>15602</v>
+        <v>7229</v>
       </c>
       <c r="H4" t="n">
-        <v>36690</v>
+        <v>17965</v>
       </c>
       <c r="I4" t="n">
-        <v>2180</v>
+        <v>1141</v>
       </c>
       <c r="J4" t="n">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="K4" t="n">
-        <v>1973844</v>
+        <v>755520</v>
       </c>
       <c r="L4" t="n">
-        <v>2844881</v>
+        <v>989832</v>
       </c>
       <c r="M4" t="n">
-        <v>907236</v>
+        <v>305552</v>
       </c>
       <c r="N4" t="n">
-        <v>138025</v>
+        <v>51940</v>
       </c>
       <c r="O4" t="n">
-        <v>444516</v>
+        <v>166521</v>
       </c>
       <c r="P4" t="n">
-        <v>97269</v>
+        <v>31880</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999972581863403</v>
+        <v>0.9999966621398926</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9218462705612183</v>
+        <v>0.8570398092269897</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8396097421646118</v>
+        <v>0.711742639541626</v>
       </c>
       <c r="T4" t="n">
-        <v>0.773128867149353</v>
+        <v>0.6025079488754272</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4838054180145264</v>
+        <v>0.2360503077507019</v>
       </c>
       <c r="V4" t="n">
-        <v>0.828901469707489</v>
+        <v>0.682550311088562</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8659578561782837</v>
+        <v>0.7236331701278687</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1020717</v>
+        <v>204872</v>
       </c>
       <c r="Z4" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AA4" t="n">
-        <v>414267</v>
+        <v>82914</v>
       </c>
       <c r="AB4" t="n">
-        <v>27445</v>
+        <v>5508</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1093320</v>
+        <v>219460</v>
       </c>
       <c r="AG4" t="n">
-        <v>1446268</v>
+        <v>289970</v>
       </c>
       <c r="AH4" t="n">
-        <v>661122</v>
+        <v>132399</v>
       </c>
       <c r="AI4" t="n">
-        <v>150368</v>
+        <v>30165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249384</v>
+        <v>49965</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570613503456116</v>
+        <v>0.9568496942520142</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106451869010925</v>
+        <v>0.9106615781784058</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578459620475769</v>
+        <v>0.8576502799987793</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620790362358093</v>
+        <v>0.6615447402000427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018246531486511</v>
+        <v>0.901755690574646</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>69006</v>
+        <v>27700</v>
       </c>
       <c r="E5" t="n">
-        <v>789570</v>
+        <v>268500</v>
       </c>
       <c r="F5" t="n">
-        <v>3509083</v>
+        <v>534164</v>
       </c>
       <c r="G5" t="n">
-        <v>56809</v>
+        <v>19674</v>
       </c>
       <c r="H5" t="n">
-        <v>223627</v>
+        <v>77340</v>
       </c>
       <c r="I5" t="n">
-        <v>13193</v>
+        <v>6037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1957408</v>
+        <v>688664</v>
       </c>
       <c r="L5" t="n">
-        <v>2453419</v>
+        <v>918041</v>
       </c>
       <c r="M5" t="n">
-        <v>1152213</v>
+        <v>399255</v>
       </c>
       <c r="N5" t="n">
-        <v>259402</v>
+        <v>70363</v>
       </c>
       <c r="O5" t="n">
-        <v>429279</v>
+        <v>159289</v>
       </c>
       <c r="P5" t="n">
-        <v>154223</v>
+        <v>65675</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999978542327881</v>
+        <v>0.9999974370002747</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9518511891365051</v>
+        <v>0.9115603566169739</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9351080060005188</v>
+        <v>0.8831647634506226</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9747765064239502</v>
+        <v>0.9568386673927307</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9951324462890625</v>
+        <v>0.9925103783607483</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9892980456352234</v>
+        <v>0.980047881603241</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9969198107719421</v>
+        <v>0.9940258860588074</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40062</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>425133</v>
+        <v>85383</v>
       </c>
       <c r="AA5" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AB5" t="n">
-        <v>49729</v>
+        <v>9974</v>
       </c>
       <c r="AC5" t="n">
-        <v>145659</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1066983</v>
+        <v>213804</v>
       </c>
       <c r="AG5" t="n">
-        <v>1468497</v>
+        <v>294510</v>
       </c>
       <c r="AH5" t="n">
-        <v>663748</v>
+        <v>133227</v>
       </c>
       <c r="AI5" t="n">
-        <v>150705</v>
+        <v>30232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250399</v>
+        <v>50139</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973541259765625</v>
+        <v>0.9734675884246826</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964300811290741</v>
+        <v>0.9642073512077332</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983773410320282</v>
+        <v>0.9837334752082825</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963125586509705</v>
+        <v>0.9963013529777527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938787817955017</v>
+        <v>0.9938697814941406</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983751177787781</v>
+        <v>0.998373806476593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>41990</v>
+        <v>14260</v>
       </c>
       <c r="E6" t="n">
-        <v>80929</v>
+        <v>20272</v>
       </c>
       <c r="F6" t="n">
-        <v>91448</v>
+        <v>23197</v>
       </c>
       <c r="G6" t="n">
-        <v>186245</v>
+        <v>18895</v>
       </c>
       <c r="H6" t="n">
-        <v>42117</v>
+        <v>11653</v>
       </c>
       <c r="I6" t="n">
-        <v>2868</v>
+        <v>966</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32262</v>
+        <v>6482</v>
       </c>
       <c r="Z6" t="n">
-        <v>26748</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>54395</v>
+        <v>10913</v>
       </c>
       <c r="AB6" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AC6" t="n">
-        <v>34895</v>
+        <v>6990</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>423</v>
+        <v>346</v>
       </c>
       <c r="E7" t="n">
-        <v>41419</v>
+        <v>22964</v>
       </c>
       <c r="F7" t="n">
-        <v>248367</v>
+        <v>89456</v>
       </c>
       <c r="G7" t="n">
-        <v>60041</v>
+        <v>22811</v>
       </c>
       <c r="H7" t="n">
-        <v>2116587</v>
+        <v>350263</v>
       </c>
       <c r="I7" t="n">
-        <v>78979</v>
+        <v>23712</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4050</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148103</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37897</v>
+        <v>7593</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>2032</v>
+        <v>1142</v>
       </c>
       <c r="F8" t="n">
-        <v>8364</v>
+        <v>4221</v>
       </c>
       <c r="G8" t="n">
-        <v>3043</v>
+        <v>1504</v>
       </c>
       <c r="H8" t="n">
-        <v>140632</v>
+        <v>58751</v>
       </c>
       <c r="I8" t="n">
-        <v>812362</v>
+        <v>127718</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
